--- a/B3_mask輔助對照_11n.xlsx
+++ b/B3_mask輔助對照_11n.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="逐顆牙對照" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="視覺化圖例" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="長度vsGT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="視覺化圖例" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X68"/>
+  <dimension ref="A1:AF68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,90 +451,130 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>剔除碎塊數</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>選取方式</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GT格式</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>兩法選取一致</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mask_IoU_vs_GT框</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>次佳mask_IoU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>長軸解釋比</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>牙位</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>方向依據</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>寬度法方向一致</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>兩端寬度比</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>AB長度_mask幾何_letterbox px</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>AB長度_mask幾何_原圖px</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>冠寬_letterbox px</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>冠寬_原圖px</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>冠寬位置_距A端比例</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>長寬比_mask幾何÷冠寬</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>真實AB像素長度_letterbox px</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>真實AB像素長度_原圖px</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>AB長度絕對誤差_letterbox px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>AB長度絕對誤差_原圖px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>幾何端點誤差_A側px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>幾何端點誤差_B側px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>A端判定與GT一致</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>QC備註</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>建議人工複查</t>
         </is>
@@ -562,66 +603,92 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>0.977</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.784</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="N2" t="n">
         <v>22</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>2.428</v>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>609.3398</v>
+        <v>2.43</v>
       </c>
       <c r="R2" t="n">
-        <v>492.2323</v>
+        <v>609.3892</v>
       </c>
       <c r="S2" t="n">
+        <v>492.2722</v>
+      </c>
+      <c r="T2" t="n">
         <v>190</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>153.4844</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.152</v>
-      </c>
       <c r="V2" t="n">
-        <v>3.2071</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
+        <v>0.149</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.2073</v>
+      </c>
+      <c r="X2" t="n">
+        <v>608.7152</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>491.7277</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -650,70 +717,96 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>0.9379999999999999</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>11</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>2.176</v>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>583.9482</v>
+        <v>2.162</v>
       </c>
       <c r="R3" t="n">
-        <v>718.9862000000001</v>
+        <v>585.5445999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>248</v>
+        <v>720.9518</v>
       </c>
       <c r="T3" t="n">
-        <v>305.35</v>
+        <v>249</v>
       </c>
       <c r="U3" t="n">
-        <v>0.106</v>
+        <v>306.5813</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3546</v>
-      </c>
-      <c r="W3" t="inlineStr">
+        <v>0.112</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.3516</v>
+      </c>
+      <c r="X3" t="n">
+        <v>599.5687</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>738.2189</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>14.024</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>17.2671</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>牙形不夠細長</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -742,66 +835,92 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>0.976</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="N4" t="n">
         <v>21</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>2.565</v>
       </c>
-      <c r="Q4" t="n">
-        <v>609.0538</v>
-      </c>
       <c r="R4" t="n">
-        <v>915.484</v>
+        <v>609.1973</v>
       </c>
       <c r="S4" t="n">
+        <v>915.6997</v>
+      </c>
+      <c r="T4" t="n">
         <v>204</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>306.6375</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.109</v>
       </c>
-      <c r="V4" t="n">
-        <v>2.9856</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="n">
+        <v>2.9863</v>
+      </c>
+      <c r="X4" t="n">
+        <v>611.223</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>918.7445</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.0256</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.0448</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -830,70 +949,96 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9360000000000001</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="N5" t="n">
         <v>31</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>2.419</v>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>590.6245</v>
+        <v>2.411</v>
       </c>
       <c r="R5" t="n">
-        <v>700.4437</v>
+        <v>591.414</v>
       </c>
       <c r="S5" t="n">
+        <v>701.38</v>
+      </c>
+      <c r="T5" t="n">
         <v>166</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>196.8656</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.052</v>
       </c>
-      <c r="V5" t="n">
-        <v>3.558</v>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="W5" t="n">
+        <v>3.5627</v>
+      </c>
+      <c r="X5" t="n">
+        <v>591.8081</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>701.8474</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -922,66 +1067,92 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>0.951</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="N6" t="n">
         <v>22</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>2.689</v>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>627.5332</v>
+        <v>2.699</v>
       </c>
       <c r="R6" t="n">
-        <v>784.4166</v>
+        <v>627.2963999999999</v>
       </c>
       <c r="S6" t="n">
+        <v>784.1205</v>
+      </c>
+      <c r="T6" t="n">
         <v>209</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>261.25</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.16</v>
-      </c>
       <c r="V6" t="n">
-        <v>3.0026</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
+        <v>0.156</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.0014</v>
+      </c>
+      <c r="X6" t="n">
+        <v>605.2080999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>756.5101</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>22.0883</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>27.6104</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1010,66 +1181,92 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.944</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.727</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="N7" t="n">
         <v>21</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>2.485</v>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q7" t="n">
-        <v>582.7578999999999</v>
+        <v>2.464</v>
       </c>
       <c r="R7" t="n">
-        <v>845.9095</v>
+        <v>583.1715</v>
       </c>
       <c r="S7" t="n">
+        <v>846.5099</v>
+      </c>
+      <c r="T7" t="n">
         <v>219</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>317.8922</v>
       </c>
-      <c r="U7" t="n">
-        <v>0.137</v>
-      </c>
       <c r="V7" t="n">
-        <v>2.661</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
+        <v>0.146</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.6629</v>
+      </c>
+      <c r="X7" t="n">
+        <v>596.3623</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>865.6572</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13.1908</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>19.1472</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1098,66 +1295,92 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>0.953</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="N8" t="n">
         <v>11</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1.967</v>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q8" t="n">
-        <v>614.0248</v>
+        <v>1.959</v>
       </c>
       <c r="R8" t="n">
-        <v>921.0373</v>
+        <v>614.348</v>
       </c>
       <c r="S8" t="n">
+        <v>921.522</v>
+      </c>
+      <c r="T8" t="n">
         <v>174</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>261</v>
       </c>
-      <c r="U8" t="n">
-        <v>0.12</v>
-      </c>
       <c r="V8" t="n">
-        <v>3.5289</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
+        <v>0.112</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.5307</v>
+      </c>
+      <c r="X8" t="n">
+        <v>613.4721</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>920.2080999999999</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1186,66 +1409,92 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.946</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="L9" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="N9" t="n">
         <v>12</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>2.258</v>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>600.8243</v>
+        <v>2.249</v>
       </c>
       <c r="R9" t="n">
-        <v>462.8224</v>
+        <v>601.0105</v>
       </c>
       <c r="S9" t="n">
-        <v>185</v>
+        <v>462.9659</v>
       </c>
       <c r="T9" t="n">
-        <v>142.5078</v>
+        <v>186</v>
       </c>
       <c r="U9" t="n">
-        <v>0.13</v>
+        <v>143.2781</v>
       </c>
       <c r="V9" t="n">
-        <v>3.2477</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
+        <v>0.151</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.2312</v>
+      </c>
+      <c r="X9" t="n">
+        <v>597.0218</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>459.8934</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.9887</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.0725</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1274,66 +1523,92 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>0.963</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N10" t="n">
         <v>12</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>1.954</v>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q10" t="n">
-        <v>607.2218</v>
+        <v>1.946</v>
       </c>
       <c r="R10" t="n">
-        <v>1559.8009</v>
+        <v>607.854</v>
       </c>
       <c r="S10" t="n">
-        <v>198</v>
+        <v>1561.4248</v>
       </c>
       <c r="T10" t="n">
-        <v>508.6125</v>
+        <v>197.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.139</v>
+        <v>507.3281</v>
       </c>
       <c r="V10" t="n">
-        <v>3.0668</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
+        <v>0.165</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.0777</v>
+      </c>
+      <c r="X10" t="n">
+        <v>620.7621</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1594.5826</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12.9081</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>33.1577</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1362,70 +1637,96 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>0.959</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="N11" t="n">
         <v>41</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>2.507</v>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q11" t="n">
-        <v>576.9731</v>
+        <v>2.509</v>
       </c>
       <c r="R11" t="n">
-        <v>382.2447</v>
+        <v>577.296</v>
       </c>
       <c r="S11" t="n">
+        <v>382.4586</v>
+      </c>
+      <c r="T11" t="n">
         <v>179</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>118.5875</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.051</v>
       </c>
-      <c r="V11" t="n">
-        <v>3.2233</v>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="n">
+        <v>3.2251</v>
+      </c>
+      <c r="X11" t="n">
+        <v>576.8697</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>382.1762</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -1454,66 +1755,92 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>0.904</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N12" t="n">
         <v>21</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>2.268</v>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q12" t="n">
-        <v>580.8473</v>
+        <v>2.267</v>
       </c>
       <c r="R12" t="n">
-        <v>869.4558</v>
+        <v>580.9856</v>
       </c>
       <c r="S12" t="n">
+        <v>869.6629</v>
+      </c>
+      <c r="T12" t="n">
         <v>207</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>309.8531</v>
       </c>
-      <c r="U12" t="n">
-        <v>0.132</v>
-      </c>
       <c r="V12" t="n">
-        <v>2.806</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
+        <v>0.134</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.8067</v>
+      </c>
+      <c r="X12" t="n">
+        <v>624.004</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>934.056</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>43.0184</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>64.39319999999999</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1542,66 +1869,92 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0.978</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.748</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="N13" t="n">
         <v>22</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>2.178</v>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q13" t="n">
-        <v>593.4926</v>
+        <v>2.249</v>
       </c>
       <c r="R13" t="n">
-        <v>799.3603000000001</v>
+        <v>560.9398</v>
       </c>
       <c r="S13" t="n">
-        <v>196</v>
+        <v>755.5157</v>
       </c>
       <c r="T13" t="n">
-        <v>263.9875</v>
+        <v>194</v>
       </c>
       <c r="U13" t="n">
-        <v>0.159</v>
+        <v>261.2937</v>
       </c>
       <c r="V13" t="n">
-        <v>3.028</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
+        <v>0.108</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.8914</v>
+      </c>
+      <c r="X13" t="n">
+        <v>592.8066</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>798.4365</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>31.8669</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>42.9207</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1630,66 +1983,92 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.766</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="N14" t="n">
         <v>11</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
         <v>1.914</v>
       </c>
-      <c r="Q14" t="n">
-        <v>598.3284</v>
-      </c>
       <c r="R14" t="n">
-        <v>816.1573</v>
+        <v>598.2098</v>
       </c>
       <c r="S14" t="n">
-        <v>193</v>
+        <v>815.9955</v>
       </c>
       <c r="T14" t="n">
-        <v>263.2641</v>
+        <v>192</v>
       </c>
       <c r="U14" t="n">
-        <v>0.126</v>
+        <v>261.9</v>
       </c>
       <c r="V14" t="n">
-        <v>3.1001</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
+        <v>0.116</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.1157</v>
+      </c>
+      <c r="X14" t="n">
+        <v>608.904</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>830.5830999999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10.6942</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>14.5876</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1718,66 +2097,92 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>0.954</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="N15" t="n">
         <v>31</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1.303</v>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q15" t="n">
-        <v>601.2035</v>
+        <v>1.308</v>
       </c>
       <c r="R15" t="n">
-        <v>710.1716</v>
+        <v>601.4763</v>
       </c>
       <c r="S15" t="n">
-        <v>147</v>
+        <v>710.4939000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>173.6437</v>
+        <v>148</v>
       </c>
       <c r="U15" t="n">
-        <v>0.264</v>
+        <v>174.825</v>
       </c>
       <c r="V15" t="n">
-        <v>4.0898</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
+        <v>0.27</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.064</v>
+      </c>
+      <c r="X15" t="n">
+        <v>599.0377999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>707.6135</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.4385</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.8805</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1806,66 +2211,92 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>0.973</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="N16" t="n">
         <v>31</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1.951</v>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q16" t="n">
-        <v>588.592</v>
+        <v>1.922</v>
       </c>
       <c r="R16" t="n">
-        <v>741.2581</v>
+        <v>590.3785</v>
       </c>
       <c r="S16" t="n">
-        <v>129</v>
+        <v>743.5078999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>162.4594</v>
+        <v>128</v>
       </c>
       <c r="U16" t="n">
-        <v>0.258</v>
+        <v>161.2</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5627</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
+        <v>0.259</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.6123</v>
+      </c>
+      <c r="X16" t="n">
+        <v>595.4134</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>749.8488</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.3409</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1894,66 +2325,92 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>0.949</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="N17" t="n">
         <v>31</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2.078</v>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>607.3711</v>
+        <v>2.061</v>
       </c>
       <c r="R17" t="n">
-        <v>1356.1457</v>
+        <v>608.7825</v>
       </c>
       <c r="S17" t="n">
-        <v>142.5</v>
+        <v>1359.2972</v>
       </c>
       <c r="T17" t="n">
-        <v>318.1758</v>
+        <v>142</v>
       </c>
       <c r="U17" t="n">
-        <v>0.128</v>
+        <v>317.0594</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2623</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
+        <v>0.116</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.2872</v>
+      </c>
+      <c r="X17" t="n">
+        <v>608.1827</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1357.9579</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.3393</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1982,66 +2439,92 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>0.9379999999999999</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2.233</v>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>606.8867</v>
+        <v>2.262</v>
       </c>
       <c r="R18" t="n">
-        <v>1782.7297</v>
+        <v>606.3561999999999</v>
       </c>
       <c r="S18" t="n">
+        <v>1781.1712</v>
+      </c>
+      <c r="T18" t="n">
         <v>198</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>581.625</v>
       </c>
-      <c r="U18" t="n">
-        <v>0.159</v>
-      </c>
       <c r="V18" t="n">
-        <v>3.0651</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
+        <v>0.154</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.0624</v>
+      </c>
+      <c r="X18" t="n">
+        <v>613.0415</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1800.8094</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.6854</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>19.6382</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2070,66 +2553,92 @@
       <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>0.969</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.771</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="N19" t="n">
         <v>22</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1.967</v>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q19" t="n">
-        <v>610.5017</v>
+        <v>1.968</v>
       </c>
       <c r="R19" t="n">
-        <v>812.7304</v>
+        <v>610.7604</v>
       </c>
       <c r="S19" t="n">
+        <v>813.0748</v>
+      </c>
+      <c r="T19" t="n">
         <v>188</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>250.275</v>
       </c>
-      <c r="U19" t="n">
-        <v>0.129</v>
-      </c>
       <c r="V19" t="n">
-        <v>3.2473</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
+        <v>0.144</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.2487</v>
+      </c>
+      <c r="X19" t="n">
+        <v>600.848</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>799.8789</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9.9124</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>13.1959</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2158,68 +2667,98 @@
       <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0.982</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.975</v>
       </c>
       <c r="L20" t="n">
-        <v>0.783</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="N20" t="n">
         <v>11</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>2.576</v>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>603.4283</v>
+        <v>2.573</v>
       </c>
       <c r="R20" t="n">
-        <v>910.7995</v>
+        <v>603.9124</v>
       </c>
       <c r="S20" t="n">
-        <v>188</v>
+        <v>911.5303</v>
       </c>
       <c r="T20" t="n">
-        <v>283.7625</v>
+        <v>187</v>
       </c>
       <c r="U20" t="n">
-        <v>0.101</v>
+        <v>282.2531</v>
       </c>
       <c r="V20" t="n">
-        <v>3.2097</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>否</t>
+        <v>0.095</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.2295</v>
+      </c>
+      <c r="X20" t="n">
+        <v>607.0512</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>916.2679000000001</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.1388</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.7376</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
         </is>
       </c>
     </row>
@@ -2246,68 +2785,98 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>0.948</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.718</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="N21" t="n">
         <v>11</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>2.101</v>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>592.1581</v>
+        <v>2.091</v>
       </c>
       <c r="R21" t="n">
-        <v>416.3611</v>
+        <v>593.6866</v>
       </c>
       <c r="S21" t="n">
+        <v>417.4359</v>
+      </c>
+      <c r="T21" t="n">
         <v>229</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>161.0156</v>
       </c>
-      <c r="U21" t="n">
-        <v>0.149</v>
-      </c>
       <c r="V21" t="n">
-        <v>2.5858</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>否</t>
+        <v>0.146</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.5925</v>
+      </c>
+      <c r="X21" t="n">
+        <v>581.5178</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>408.8797</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>12.1688</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8.5562</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>牙形不夠細長</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
         </is>
       </c>
     </row>
@@ -2334,66 +2903,92 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>0.952</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.764</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="N22" t="n">
         <v>12</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>2.162</v>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q22" t="n">
-        <v>611.605</v>
+        <v>2.161</v>
       </c>
       <c r="R22" t="n">
-        <v>753.0386999999999</v>
+        <v>611.67</v>
       </c>
       <c r="S22" t="n">
-        <v>204</v>
+        <v>753.1187</v>
       </c>
       <c r="T22" t="n">
-        <v>251.175</v>
+        <v>204.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0.152</v>
+        <v>251.7906</v>
       </c>
       <c r="V22" t="n">
-        <v>2.9981</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
+        <v>0.161</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.9911</v>
+      </c>
+      <c r="X22" t="n">
+        <v>631.221</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>777.1908</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>19.5509</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>24.0721</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2422,66 +3017,92 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>0.951</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.768</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="N23" t="n">
         <v>11</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>2.376</v>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>617.2453</v>
+        <v>2.367</v>
       </c>
       <c r="R23" t="n">
-        <v>837.139</v>
+        <v>618.1136</v>
       </c>
       <c r="S23" t="n">
-        <v>209</v>
+        <v>838.3166</v>
       </c>
       <c r="T23" t="n">
-        <v>283.4563</v>
+        <v>208</v>
       </c>
       <c r="U23" t="n">
-        <v>0.122</v>
+        <v>282.1</v>
       </c>
       <c r="V23" t="n">
-        <v>2.9533</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
+        <v>0.123</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.9717</v>
+      </c>
+      <c r="X23" t="n">
+        <v>612.4829</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>830.6799</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.6307</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7.6367</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2510,70 +3131,96 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>0.975</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="N24" t="n">
         <v>21</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>2.542</v>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>594.4774</v>
+        <v>2.572</v>
       </c>
       <c r="R24" t="n">
-        <v>708.7285000000001</v>
+        <v>593.8708</v>
       </c>
       <c r="S24" t="n">
+        <v>708.0054</v>
+      </c>
+      <c r="T24" t="n">
         <v>261</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>311.1609</v>
       </c>
-      <c r="U24" t="n">
-        <v>0.152</v>
-      </c>
       <c r="V24" t="n">
-        <v>2.2777</v>
-      </c>
-      <c r="W24" t="inlineStr">
+        <v>0.149</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.2754</v>
+      </c>
+      <c r="X24" t="n">
+        <v>594.7218</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>709.0199</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.0145</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>牙形不夠細長</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -2602,66 +3249,92 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>0.954</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="N25" t="n">
         <v>22</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1.894</v>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q25" t="n">
-        <v>598.4576</v>
+        <v>1.908</v>
       </c>
       <c r="R25" t="n">
-        <v>696.6421</v>
+        <v>598.0988</v>
       </c>
       <c r="S25" t="n">
-        <v>223</v>
+        <v>696.2243999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>259.5859</v>
+        <v>223.5</v>
       </c>
       <c r="U25" t="n">
+        <v>260.168</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.178</v>
       </c>
-      <c r="V25" t="n">
-        <v>2.6837</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
+      <c r="W25" t="n">
+        <v>2.6761</v>
+      </c>
+      <c r="X25" t="n">
+        <v>592.4369</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>689.6336</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.6619</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>6.5908</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2690,70 +3363,96 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>0.978</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="N26" t="n">
         <v>21</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
         <v>2.172</v>
       </c>
-      <c r="Q26" t="n">
-        <v>608.9213</v>
-      </c>
       <c r="R26" t="n">
-        <v>831.5581</v>
+        <v>608.924</v>
       </c>
       <c r="S26" t="n">
+        <v>831.5617999999999</v>
+      </c>
+      <c r="T26" t="n">
         <v>233</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>318.1906</v>
       </c>
-      <c r="U26" t="n">
-        <v>0.091</v>
-      </c>
       <c r="V26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.6134</v>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="n">
+        <v>602.66</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>823.0076</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.2639</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>8.5541</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -2782,70 +3481,96 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0.88</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.879</v>
       </c>
       <c r="L27" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="N27" t="n">
         <v>11</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>2.281</v>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q27" t="n">
-        <v>579.3402</v>
+        <v>2.323</v>
       </c>
       <c r="R27" t="n">
-        <v>758.5735</v>
+        <v>577.1343000000001</v>
       </c>
       <c r="S27" t="n">
+        <v>755.6852</v>
+      </c>
+      <c r="T27" t="n">
         <v>200</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>261.875</v>
       </c>
-      <c r="U27" t="n">
-        <v>0.08400000000000001</v>
-      </c>
       <c r="V27" t="n">
-        <v>2.8967</v>
-      </c>
-      <c r="W27" t="inlineStr">
+        <v>0.074</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.8857</v>
+      </c>
+      <c r="X27" t="n">
+        <v>595.9450000000001</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>780.3155</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>18.8107</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>24.6303</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -2874,66 +3599,92 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>0.951</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="N28" t="n">
         <v>21</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>2.173</v>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q28" t="n">
-        <v>635.3407</v>
+        <v>2.182</v>
       </c>
       <c r="R28" t="n">
-        <v>850.7609</v>
+        <v>634.3194</v>
       </c>
       <c r="S28" t="n">
+        <v>849.3934</v>
+      </c>
+      <c r="T28" t="n">
         <v>218</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>291.9156</v>
       </c>
-      <c r="U28" t="n">
-        <v>0.108</v>
-      </c>
       <c r="V28" t="n">
-        <v>2.9144</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr">
+        <v>0.102</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.9097</v>
+      </c>
+      <c r="X28" t="n">
+        <v>607.0013</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>812.8126999999999</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>27.3181</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>36.5807</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2962,66 +3713,92 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>0.986</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.744</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="N29" t="n">
         <v>11</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>2.036</v>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q29" t="n">
-        <v>597.6399</v>
+        <v>2.04</v>
       </c>
       <c r="R29" t="n">
-        <v>428.6198</v>
+        <v>597.4206</v>
       </c>
       <c r="S29" t="n">
+        <v>428.4626</v>
+      </c>
+      <c r="T29" t="n">
         <v>219</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>157.0641</v>
       </c>
-      <c r="U29" t="n">
-        <v>0.172</v>
-      </c>
       <c r="V29" t="n">
-        <v>2.7289</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
+        <v>0.167</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.7279</v>
+      </c>
+      <c r="X29" t="n">
+        <v>597.3341</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>428.4005</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3050,66 +3827,92 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>0.9370000000000001</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="N30" t="n">
         <v>21</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>2.301</v>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>603.7898</v>
+        <v>2.299</v>
       </c>
       <c r="R30" t="n">
-        <v>834.9281</v>
+        <v>604.2424999999999</v>
       </c>
       <c r="S30" t="n">
+        <v>835.554</v>
+      </c>
+      <c r="T30" t="n">
         <v>220</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>304.2188</v>
       </c>
-      <c r="U30" t="n">
-        <v>0.135</v>
-      </c>
       <c r="V30" t="n">
-        <v>2.7445</v>
-      </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr">
+        <v>0.137</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.7466</v>
+      </c>
+      <c r="X30" t="n">
+        <v>609.8621000000001</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>843.3249</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.6197</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>7.7709</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3138,66 +3941,92 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>0.981</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="N31" t="n">
         <v>21</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>2.421</v>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>613.9414</v>
+        <v>2.457</v>
       </c>
       <c r="R31" t="n">
-        <v>1636.5374</v>
+        <v>613.2809999999999</v>
       </c>
       <c r="S31" t="n">
+        <v>1634.7772</v>
+      </c>
+      <c r="T31" t="n">
         <v>215</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>573.1094000000001</v>
       </c>
-      <c r="U31" t="n">
-        <v>0.105</v>
-      </c>
       <c r="V31" t="n">
-        <v>2.8555</v>
-      </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr">
+        <v>0.149</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.8525</v>
+      </c>
+      <c r="X31" t="n">
+        <v>620.7604</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1654.7146</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7.4794</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>19.9374</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3226,66 +4055,92 @@
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>0.972</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="N32" t="n">
         <v>11</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>2.291</v>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>617.7781</v>
+        <v>2.298</v>
       </c>
       <c r="R32" t="n">
-        <v>1616.8412</v>
+        <v>617.439</v>
       </c>
       <c r="S32" t="n">
+        <v>1615.9537</v>
+      </c>
+      <c r="T32" t="n">
         <v>210</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>549.6094000000001</v>
       </c>
-      <c r="U32" t="n">
-        <v>0.132</v>
-      </c>
       <c r="V32" t="n">
-        <v>2.9418</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr">
+        <v>0.137</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.9402</v>
+      </c>
+      <c r="X32" t="n">
+        <v>624.2833000000001</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1633.8663</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.8442</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>17.9126</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3314,66 +4169,92 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>0.98</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="N33" t="n">
         <v>22</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>2.092</v>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q33" t="n">
-        <v>598.1673</v>
+        <v>2.105</v>
       </c>
       <c r="R33" t="n">
-        <v>1630.0059</v>
+        <v>599.8022999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>166</v>
+        <v>1634.4613</v>
       </c>
       <c r="T33" t="n">
-        <v>452.35</v>
+        <v>165.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0.103</v>
+        <v>450.9875</v>
       </c>
       <c r="V33" t="n">
-        <v>3.6034</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
+        <v>0.118</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.6242</v>
+      </c>
+      <c r="X33" t="n">
+        <v>599.2941</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1633.0763</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3402,70 +4283,96 @@
       <c r="F34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="N34" t="n">
         <v>12</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>1.636</v>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q34" t="n">
-        <v>596.1396</v>
+        <v>1.64</v>
       </c>
       <c r="R34" t="n">
-        <v>728.4081</v>
+        <v>595.827</v>
       </c>
       <c r="S34" t="n">
+        <v>728.0262</v>
+      </c>
+      <c r="T34" t="n">
         <v>166</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>202.8313</v>
       </c>
-      <c r="U34" t="n">
-        <v>0.058</v>
-      </c>
       <c r="V34" t="n">
-        <v>3.5912</v>
-      </c>
-      <c r="W34" t="inlineStr">
+        <v>0.051</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.5893</v>
+      </c>
+      <c r="X34" t="n">
+        <v>594.3914</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>726.272</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.4356</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.7542</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -3494,66 +4401,92 @@
       <c r="F35" t="n">
         <v>1</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>0.976</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
-        <v>0.742</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="N35" t="n">
         <v>21</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>2.422</v>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q35" t="n">
-        <v>597.0558</v>
+        <v>2.423</v>
       </c>
       <c r="R35" t="n">
-        <v>745.3868</v>
+        <v>597.0170000000001</v>
       </c>
       <c r="S35" t="n">
+        <v>745.3384</v>
+      </c>
+      <c r="T35" t="n">
         <v>223</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>278.4016</v>
       </c>
-      <c r="U35" t="n">
-        <v>0.113</v>
-      </c>
       <c r="V35" t="n">
-        <v>2.6774</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr">
+        <v>0.115</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.6772</v>
+      </c>
+      <c r="X35" t="n">
+        <v>592.4417999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>739.6265</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.5752</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.7118</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3582,66 +4515,92 @@
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>0.877</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="N36" t="n">
         <v>22</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>1.159</v>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q36" t="n">
-        <v>624.4486000000001</v>
+        <v>1.148</v>
       </c>
       <c r="R36" t="n">
-        <v>756.1682</v>
+        <v>620.1271</v>
       </c>
       <c r="S36" t="n">
-        <v>198</v>
+        <v>750.9352</v>
       </c>
       <c r="T36" t="n">
-        <v>239.7656</v>
+        <v>199</v>
       </c>
       <c r="U36" t="n">
-        <v>0.191</v>
+        <v>240.9766</v>
       </c>
       <c r="V36" t="n">
-        <v>3.1538</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
+        <v>0.193</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.1162</v>
+      </c>
+      <c r="X36" t="n">
+        <v>595.9891</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>721.7056</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>24.138</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>29.2296</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3670,70 +4629,96 @@
       <c r="F37" t="n">
         <v>1</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>0.986</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
-        <v>0.763</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="N37" t="n">
         <v>11</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>2.092</v>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q37" t="n">
-        <v>625.5621</v>
+        <v>2.1</v>
       </c>
       <c r="R37" t="n">
-        <v>911.9521999999999</v>
+        <v>626.3587</v>
       </c>
       <c r="S37" t="n">
+        <v>913.1136</v>
+      </c>
+      <c r="T37" t="n">
         <v>202</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>294.4781</v>
       </c>
-      <c r="U37" t="n">
-        <v>0.08400000000000001</v>
-      </c>
       <c r="V37" t="n">
-        <v>3.0968</v>
-      </c>
-      <c r="W37" t="inlineStr">
+        <v>0.081</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.1008</v>
+      </c>
+      <c r="X37" t="n">
+        <v>626.5896</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>913.4502</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -3762,70 +4747,96 @@
       <c r="F38" t="n">
         <v>1</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>0.873</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="N38" t="n">
         <v>21</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>2.145</v>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q38" t="n">
-        <v>596.2485</v>
+        <v>2.118</v>
       </c>
       <c r="R38" t="n">
-        <v>723.8828999999999</v>
+        <v>597.8584</v>
       </c>
       <c r="S38" t="n">
+        <v>725.8374</v>
+      </c>
+      <c r="T38" t="n">
         <v>228</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>276.8063</v>
       </c>
-      <c r="U38" t="n">
-        <v>0.08799999999999999</v>
-      </c>
       <c r="V38" t="n">
-        <v>2.6151</v>
-      </c>
-      <c r="W38" t="inlineStr">
+        <v>0.095</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.6222</v>
+      </c>
+      <c r="X38" t="n">
+        <v>597.8243</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>725.7961</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -3854,70 +4865,96 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>0.965</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.753</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="N39" t="n">
         <v>21</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>2.306</v>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>604.6856</v>
+        <v>2.307</v>
       </c>
       <c r="R39" t="n">
-        <v>839.0013</v>
+        <v>604.6218</v>
       </c>
       <c r="S39" t="n">
+        <v>838.9127999999999</v>
+      </c>
+      <c r="T39" t="n">
         <v>215</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>298.3125</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.064</v>
       </c>
-      <c r="V39" t="n">
-        <v>2.8125</v>
-      </c>
-      <c r="W39" t="inlineStr">
+      <c r="W39" t="n">
+        <v>2.8122</v>
+      </c>
+      <c r="X39" t="n">
+        <v>608.1676</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>843.8326</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.5458</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.9198</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AF39" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -3946,66 +4983,92 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>0.919</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="N40" t="n">
         <v>22</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>1.047</v>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q40" t="n">
-        <v>618.615</v>
+        <v>1.066</v>
       </c>
       <c r="R40" t="n">
-        <v>1436.3468</v>
+        <v>624.4481</v>
       </c>
       <c r="S40" t="n">
+        <v>1449.8903</v>
+      </c>
+      <c r="T40" t="n">
         <v>163</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>378.4656</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.163</v>
       </c>
-      <c r="V40" t="n">
-        <v>3.7952</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr">
+      <c r="W40" t="n">
+        <v>3.831</v>
+      </c>
+      <c r="X40" t="n">
+        <v>609.7061</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1415.6613</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>14.742</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>34.229</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4034,66 +5097,92 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>0.965</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="N41" t="n">
         <v>12</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>2.072</v>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q41" t="n">
-        <v>609.181</v>
+        <v>2.075</v>
       </c>
       <c r="R41" t="n">
-        <v>821.4424</v>
+        <v>609.3737</v>
       </c>
       <c r="S41" t="n">
-        <v>196</v>
+        <v>821.7024</v>
       </c>
       <c r="T41" t="n">
-        <v>264.2937</v>
+        <v>197</v>
       </c>
       <c r="U41" t="n">
-        <v>0.137</v>
+        <v>265.6422</v>
       </c>
       <c r="V41" t="n">
-        <v>3.1081</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr">
+        <v>0.141</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.0933</v>
+      </c>
+      <c r="X41" t="n">
+        <v>595.6709</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>803.225</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>13.7028</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>18.4774</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4122,70 +5211,96 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>0.9340000000000001</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
-        <v>0.792</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="N42" t="n">
         <v>31</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>2.17</v>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q42" t="n">
-        <v>604.3246</v>
+        <v>2.163</v>
       </c>
       <c r="R42" t="n">
-        <v>417.3617</v>
+        <v>605.1048</v>
       </c>
       <c r="S42" t="n">
-        <v>163</v>
+        <v>417.9005</v>
       </c>
       <c r="T42" t="n">
-        <v>112.5719</v>
+        <v>162</v>
       </c>
       <c r="U42" t="n">
-        <v>0.08</v>
+        <v>111.8813</v>
       </c>
       <c r="V42" t="n">
-        <v>3.7075</v>
-      </c>
-      <c r="W42" t="inlineStr">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.7352</v>
+      </c>
+      <c r="X42" t="n">
+        <v>593.482</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>409.8735</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>11.6228</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.026999999999999</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AF42" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -4214,66 +5329,92 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0.945</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="L43" t="n">
-        <v>0.806</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="N43" t="n">
         <v>32</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>2.236</v>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q43" t="n">
-        <v>607.4886</v>
+        <v>2.238</v>
       </c>
       <c r="R43" t="n">
-        <v>721.3927</v>
+        <v>606.6413</v>
       </c>
       <c r="S43" t="n">
+        <v>720.3865</v>
+      </c>
+      <c r="T43" t="n">
         <v>167</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>198.3125</v>
       </c>
-      <c r="U43" t="n">
-        <v>0.117</v>
-      </c>
       <c r="V43" t="n">
-        <v>3.6377</v>
-      </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr">
+        <v>0.12</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.6326</v>
+      </c>
+      <c r="X43" t="n">
+        <v>595.4754</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>707.1271</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>11.1658</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>13.2594</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4302,70 +5443,96 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>0.968</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>0.8139999999999999</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="N44" t="n">
         <v>41</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
         <v>2.232</v>
       </c>
-      <c r="Q44" t="n">
-        <v>600.2879</v>
-      </c>
       <c r="R44" t="n">
-        <v>788.8158</v>
+        <v>600.3126</v>
       </c>
       <c r="S44" t="n">
+        <v>788.8483</v>
+      </c>
+      <c r="T44" t="n">
         <v>140</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>183.9688</v>
       </c>
-      <c r="U44" t="n">
-        <v>0.059</v>
-      </c>
       <c r="V44" t="n">
-        <v>4.2878</v>
-      </c>
-      <c r="W44" t="inlineStr">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W44" t="n">
+        <v>4.2879</v>
+      </c>
+      <c r="X44" t="n">
+        <v>599.3095</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>787.5300999999999</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.0031</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.3182</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -4394,70 +5561,96 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>0.92</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
-        <v>0.6850000000000001</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N45" t="n">
         <v>11</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>2.314</v>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q45" t="n">
-        <v>591.3717</v>
+        <v>2.291</v>
       </c>
       <c r="R45" t="n">
-        <v>697.6338</v>
+        <v>593.1554</v>
       </c>
       <c r="S45" t="n">
-        <v>268</v>
+        <v>699.7381</v>
       </c>
       <c r="T45" t="n">
-        <v>316.1562</v>
+        <v>267</v>
       </c>
       <c r="U45" t="n">
-        <v>0.121</v>
+        <v>314.9766</v>
       </c>
       <c r="V45" t="n">
-        <v>2.2066</v>
-      </c>
-      <c r="W45" t="inlineStr">
+        <v>0.119</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.2216</v>
+      </c>
+      <c r="X45" t="n">
+        <v>615.3535000000001</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>725.9249</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>22.1981</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>26.1868</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
         <is>
           <t>牙形不夠細長</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -4486,66 +5679,92 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>0.968</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
-        <v>0.738</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N46" t="n">
         <v>11</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>1.695</v>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q46" t="n">
-        <v>632.3099999999999</v>
+        <v>1.687</v>
       </c>
       <c r="R46" t="n">
-        <v>1776.3958</v>
+        <v>632.8</v>
       </c>
       <c r="S46" t="n">
+        <v>1777.7725</v>
+      </c>
+      <c r="T46" t="n">
         <v>235</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>660.2030999999999</v>
       </c>
-      <c r="U46" t="n">
-        <v>0.164</v>
-      </c>
       <c r="V46" t="n">
-        <v>2.6907</v>
-      </c>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr">
+        <v>0.17</v>
+      </c>
+      <c r="W46" t="n">
+        <v>2.6928</v>
+      </c>
+      <c r="X46" t="n">
+        <v>618.876</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1738.6547</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>13.924</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>39.1178</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4574,66 +5793,92 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>0.927</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="N47" t="n">
         <v>21</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>2.359</v>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q47" t="n">
-        <v>611.0246</v>
+        <v>2.395</v>
       </c>
       <c r="R47" t="n">
-        <v>1708.9593</v>
+        <v>610.1953999999999</v>
       </c>
       <c r="S47" t="n">
+        <v>1706.6403</v>
+      </c>
+      <c r="T47" t="n">
         <v>229</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>640.4844000000001</v>
       </c>
-      <c r="U47" t="n">
-        <v>0.166</v>
-      </c>
       <c r="V47" t="n">
-        <v>2.6682</v>
-      </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr">
+        <v>0.173</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.6646</v>
+      </c>
+      <c r="X47" t="n">
+        <v>607.6014</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1699.3852</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>7.2551</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4662,66 +5907,92 @@
       <c r="F48" t="n">
         <v>1</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>0.885</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N48" t="n">
         <v>22</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
         <v>1.617</v>
       </c>
-      <c r="Q48" t="n">
-        <v>569.3815</v>
-      </c>
       <c r="R48" t="n">
-        <v>1598.7165</v>
+        <v>569.3825000000001</v>
       </c>
       <c r="S48" t="n">
+        <v>1598.7194</v>
+      </c>
+      <c r="T48" t="n">
         <v>181</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>508.2141</v>
       </c>
-      <c r="U48" t="n">
-        <v>0.156</v>
-      </c>
       <c r="V48" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="W48" t="n">
         <v>3.1458</v>
       </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr">
+      <c r="X48" t="n">
+        <v>606.7086</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1703.524</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>37.3261</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>104.8046</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4750,66 +6021,92 @@
       <c r="F49" t="n">
         <v>1</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>0.954</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="N49" t="n">
         <v>11</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>1.809</v>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q49" t="n">
-        <v>608.7138</v>
+        <v>1.85</v>
       </c>
       <c r="R49" t="n">
-        <v>1634.0162</v>
+        <v>598.4814</v>
       </c>
       <c r="S49" t="n">
-        <v>223.5</v>
+        <v>1606.5485</v>
       </c>
       <c r="T49" t="n">
-        <v>599.9578</v>
+        <v>222.5</v>
       </c>
       <c r="U49" t="n">
-        <v>0.174</v>
+        <v>597.2734</v>
       </c>
       <c r="V49" t="n">
-        <v>2.7236</v>
-      </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr">
+        <v>0.163</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.6898</v>
+      </c>
+      <c r="X49" t="n">
+        <v>599.429</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1609.0922</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.9476</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.5437</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4838,66 +6135,92 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
         <v>0.962</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N50" t="n">
         <v>21</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>1.709</v>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q50" t="n">
-        <v>602.1448</v>
+        <v>1.675</v>
       </c>
       <c r="R50" t="n">
-        <v>1629.5543</v>
+        <v>609.4863</v>
       </c>
       <c r="S50" t="n">
-        <v>219</v>
+        <v>1649.4224</v>
       </c>
       <c r="T50" t="n">
-        <v>592.6686999999999</v>
+        <v>218</v>
       </c>
       <c r="U50" t="n">
-        <v>0.134</v>
+        <v>589.9625</v>
       </c>
       <c r="V50" t="n">
-        <v>2.7495</v>
-      </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr">
+        <v>0.181</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.7958</v>
+      </c>
+      <c r="X50" t="n">
+        <v>607.1153</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1643.0057</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.3711</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>6.4167</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4926,70 +6249,96 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
         <v>0.984</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
-        <v>0.774</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="N51" t="n">
         <v>32</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>1.997</v>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q51" t="n">
-        <v>592.0039</v>
+        <v>2.003</v>
       </c>
       <c r="R51" t="n">
-        <v>1482.7847</v>
+        <v>591.2989</v>
       </c>
       <c r="S51" t="n">
+        <v>1481.0189</v>
+      </c>
+      <c r="T51" t="n">
         <v>175</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>438.3203</v>
       </c>
-      <c r="U51" t="n">
-        <v>0.092</v>
-      </c>
       <c r="V51" t="n">
-        <v>3.3829</v>
-      </c>
-      <c r="W51" t="inlineStr">
+        <v>0.099</v>
+      </c>
+      <c r="W51" t="n">
+        <v>3.3789</v>
+      </c>
+      <c r="X51" t="n">
+        <v>592.5101</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1484.0526</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.2112</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.0337</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="AF51" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -5018,70 +6367,96 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
         <v>0.956</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N52" t="n">
         <v>31</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
         <v>2.305</v>
       </c>
-      <c r="Q52" t="n">
-        <v>615.1517</v>
-      </c>
       <c r="R52" t="n">
-        <v>1423.4996</v>
+        <v>615.1018</v>
       </c>
       <c r="S52" t="n">
-        <v>169</v>
+        <v>1423.384</v>
       </c>
       <c r="T52" t="n">
-        <v>391.0766</v>
+        <v>170</v>
       </c>
       <c r="U52" t="n">
-        <v>0.063</v>
+        <v>393.3906</v>
       </c>
       <c r="V52" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="W52" t="inlineStr">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="W52" t="n">
+        <v>3.6182</v>
+      </c>
+      <c r="X52" t="n">
+        <v>593.968</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1374.4791</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.1338</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>48.905</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="AF52" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -5110,66 +6485,92 @@
       <c r="F53" t="n">
         <v>1</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
         <v>0.947</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>0.8129999999999999</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="N53" t="n">
         <v>41</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>2.022</v>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q53" t="n">
-        <v>590.1779</v>
+        <v>1.994</v>
       </c>
       <c r="R53" t="n">
-        <v>1416.4271</v>
+        <v>594.9129</v>
       </c>
       <c r="S53" t="n">
-        <v>158</v>
+        <v>1427.791</v>
       </c>
       <c r="T53" t="n">
-        <v>379.2</v>
+        <v>157.5</v>
       </c>
       <c r="U53" t="n">
-        <v>0.103</v>
+        <v>378</v>
       </c>
       <c r="V53" t="n">
-        <v>3.7353</v>
-      </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr">
+        <v>0.132</v>
+      </c>
+      <c r="W53" t="n">
+        <v>3.7772</v>
+      </c>
+      <c r="X53" t="n">
+        <v>596.5337</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1431.6808</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.6208</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.8898</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5198,66 +6599,92 @@
       <c r="F54" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
         <v>0.967</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
-        <v>0.758</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="N54" t="n">
         <v>42</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>2.343</v>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q54" t="n">
-        <v>605.1532</v>
+        <v>2.345</v>
       </c>
       <c r="R54" t="n">
-        <v>1379.5601</v>
+        <v>605.1633</v>
       </c>
       <c r="S54" t="n">
+        <v>1379.5833</v>
+      </c>
+      <c r="T54" t="n">
         <v>207</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>471.8953</v>
       </c>
-      <c r="U54" t="n">
-        <v>0.127</v>
-      </c>
       <c r="V54" t="n">
-        <v>2.9234</v>
-      </c>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr">
+        <v>0.13</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.9235</v>
+      </c>
+      <c r="X54" t="n">
+        <v>591.1604</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1347.6609</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>14.003</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>31.9224</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5286,66 +6713,92 @@
       <c r="F55" t="n">
         <v>1</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
         <v>0.882</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>0.741</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="N55" t="n">
         <v>11</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>2.257</v>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q55" t="n">
-        <v>598.8554</v>
+        <v>2.263</v>
       </c>
       <c r="R55" t="n">
-        <v>729.855</v>
+        <v>598.4769</v>
       </c>
       <c r="S55" t="n">
-        <v>217</v>
+        <v>729.3937</v>
       </c>
       <c r="T55" t="n">
-        <v>264.4688</v>
+        <v>216</v>
       </c>
       <c r="U55" t="n">
-        <v>0.117</v>
+        <v>263.25</v>
       </c>
       <c r="V55" t="n">
-        <v>2.7597</v>
-      </c>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr">
+        <v>0.114</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.7707</v>
+      </c>
+      <c r="X55" t="n">
+        <v>602.0535</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>733.7527</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.5766</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5374,66 +6827,92 @@
       <c r="F56" t="n">
         <v>1</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
         <v>0.972</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
-        <v>0.754</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N56" t="n">
         <v>21</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>2.423</v>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q56" t="n">
-        <v>618.2173</v>
+        <v>2.355</v>
       </c>
       <c r="R56" t="n">
-        <v>834.5933</v>
+        <v>620.9734</v>
       </c>
       <c r="S56" t="n">
-        <v>217</v>
+        <v>838.3141000000001</v>
       </c>
       <c r="T56" t="n">
-        <v>292.95</v>
+        <v>216</v>
       </c>
       <c r="U56" t="n">
-        <v>0.15</v>
+        <v>291.6</v>
       </c>
       <c r="V56" t="n">
-        <v>2.8489</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr">
+        <v>0.156</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.8749</v>
+      </c>
+      <c r="X56" t="n">
+        <v>618.8153</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>835.4007</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.1581</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.9135</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5462,70 +6941,96 @@
       <c r="F57" t="n">
         <v>1</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
         <v>0.924</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
-        <v>0.783</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="N57" t="n">
         <v>41</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>2.01</v>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q57" t="n">
-        <v>602.7736</v>
+        <v>2.023</v>
       </c>
       <c r="R57" t="n">
-        <v>796.7913</v>
+        <v>601.9902</v>
       </c>
       <c r="S57" t="n">
+        <v>795.7558</v>
+      </c>
+      <c r="T57" t="n">
         <v>162</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>214.1437</v>
       </c>
-      <c r="U57" t="n">
-        <v>0.076</v>
-      </c>
       <c r="V57" t="n">
-        <v>3.7208</v>
-      </c>
-      <c r="W57" t="inlineStr">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W57" t="n">
+        <v>3.716</v>
+      </c>
+      <c r="X57" t="n">
+        <v>577.7599</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>763.7264</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>24.2303</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>32.0294</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="AF57" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -5554,66 +7059,92 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>0.956</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
-        <v>0.8110000000000001</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="N58" t="n">
         <v>12</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>1.645</v>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q58" t="n">
-        <v>619.6931</v>
+        <v>1.652</v>
       </c>
       <c r="R58" t="n">
-        <v>1335.2449</v>
+        <v>619.9801</v>
       </c>
       <c r="S58" t="n">
+        <v>1335.8633</v>
+      </c>
+      <c r="T58" t="n">
         <v>162</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>349.0594</v>
       </c>
-      <c r="U58" t="n">
-        <v>0.195</v>
-      </c>
       <c r="V58" t="n">
-        <v>3.8253</v>
-      </c>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr">
+        <v>0.19</v>
+      </c>
+      <c r="W58" t="n">
+        <v>3.827</v>
+      </c>
+      <c r="X58" t="n">
+        <v>620.0128999999999</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1335.9341</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5642,66 +7173,92 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>0.946</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="N59" t="n">
         <v>11</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>2.107</v>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q59" t="n">
-        <v>622.2347</v>
+        <v>2.121</v>
       </c>
       <c r="R59" t="n">
-        <v>831.2667</v>
+        <v>622.3141000000001</v>
       </c>
       <c r="S59" t="n">
-        <v>215</v>
+        <v>831.3727</v>
       </c>
       <c r="T59" t="n">
-        <v>287.2266</v>
+        <v>214</v>
       </c>
       <c r="U59" t="n">
-        <v>0.118</v>
+        <v>285.8906</v>
       </c>
       <c r="V59" t="n">
-        <v>2.8941</v>
-      </c>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr">
+        <v>0.109</v>
+      </c>
+      <c r="W59" t="n">
+        <v>2.908</v>
+      </c>
+      <c r="X59" t="n">
+        <v>597.0329</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>797.5987</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>25.2812</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>33.7741</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5730,66 +7287,92 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
         <v>0.921</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" t="n">
-        <v>0.742</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="N60" t="n">
         <v>21</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>1.914</v>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q60" t="n">
-        <v>579.982</v>
+        <v>1.885</v>
       </c>
       <c r="R60" t="n">
-        <v>783.8819</v>
+        <v>582.5825</v>
       </c>
       <c r="S60" t="n">
-        <v>210</v>
+        <v>787.3966</v>
       </c>
       <c r="T60" t="n">
-        <v>283.8281</v>
+        <v>208</v>
       </c>
       <c r="U60" t="n">
-        <v>0.125</v>
+        <v>281.125</v>
       </c>
       <c r="V60" t="n">
-        <v>2.7618</v>
-      </c>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr">
+        <v>0.135</v>
+      </c>
+      <c r="W60" t="n">
+        <v>2.8009</v>
+      </c>
+      <c r="X60" t="n">
+        <v>622.3308</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>841.119</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>39.7484</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>53.7224</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5818,66 +7401,92 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>0.966</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="N61" t="n">
         <v>22</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P61" t="n">
-        <v>1.654</v>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q61" t="n">
-        <v>603.6004</v>
+        <v>1.69</v>
       </c>
       <c r="R61" t="n">
-        <v>788.453</v>
+        <v>601.1448</v>
       </c>
       <c r="S61" t="n">
-        <v>164</v>
+        <v>785.2455</v>
       </c>
       <c r="T61" t="n">
-        <v>214.225</v>
+        <v>165</v>
       </c>
       <c r="U61" t="n">
-        <v>0.154</v>
+        <v>215.5312</v>
       </c>
       <c r="V61" t="n">
-        <v>3.6805</v>
-      </c>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr">
+        <v>0.136</v>
+      </c>
+      <c r="W61" t="n">
+        <v>3.6433</v>
+      </c>
+      <c r="X61" t="n">
+        <v>594.3036</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>776.3090999999999</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>6.8412</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>8.936299999999999</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5906,66 +7515,92 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>0.969</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" t="n">
-        <v>0.732</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="N62" t="n">
         <v>11</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>2.855</v>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q62" t="n">
-        <v>615.2852</v>
+        <v>2.813</v>
       </c>
       <c r="R62" t="n">
-        <v>835.442</v>
+        <v>620.5189</v>
       </c>
       <c r="S62" t="n">
-        <v>232</v>
+        <v>842.5483</v>
       </c>
       <c r="T62" t="n">
-        <v>315.0125</v>
+        <v>231</v>
       </c>
       <c r="U62" t="n">
-        <v>0.111</v>
+        <v>313.6547</v>
       </c>
       <c r="V62" t="n">
-        <v>2.6521</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr">
+        <v>0.13</v>
+      </c>
+      <c r="W62" t="n">
+        <v>2.6862</v>
+      </c>
+      <c r="X62" t="n">
+        <v>624.2281</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>847.5847</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>3.7092</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>5.0364</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5994,66 +7629,92 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0.965</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="L63" t="n">
-        <v>0.766</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="N63" t="n">
         <v>12</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>2.468</v>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q63" t="n">
-        <v>602.8771</v>
+        <v>2.465</v>
       </c>
       <c r="R63" t="n">
-        <v>823.3040999999999</v>
+        <v>602.3892</v>
       </c>
       <c r="S63" t="n">
+        <v>822.6377</v>
+      </c>
+      <c r="T63" t="n">
         <v>188</v>
       </c>
-      <c r="T63" t="n">
+      <c r="U63" t="n">
         <v>256.7375</v>
       </c>
-      <c r="U63" t="n">
-        <v>0.137</v>
-      </c>
       <c r="V63" t="n">
-        <v>3.2068</v>
-      </c>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr">
+        <v>0.128</v>
+      </c>
+      <c r="W63" t="n">
+        <v>3.2042</v>
+      </c>
+      <c r="X63" t="n">
+        <v>615.754</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>840.8891</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>13.3649</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>18.2514</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6082,66 +7743,92 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
         <v>0.971</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>0.744</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="N64" t="n">
         <v>11</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>2.095</v>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q64" t="n">
-        <v>602.8644</v>
+        <v>2.082</v>
       </c>
       <c r="R64" t="n">
-        <v>514.3187</v>
+        <v>603.8423</v>
       </c>
       <c r="S64" t="n">
+        <v>515.1529</v>
+      </c>
+      <c r="T64" t="n">
         <v>207</v>
       </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>176.5969</v>
       </c>
-      <c r="U64" t="n">
-        <v>0.142</v>
-      </c>
       <c r="V64" t="n">
-        <v>2.9124</v>
-      </c>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr">
+        <v>0.143</v>
+      </c>
+      <c r="W64" t="n">
+        <v>2.9171</v>
+      </c>
+      <c r="X64" t="n">
+        <v>599.5005</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>511.4489</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>4.3417</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>3.704</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6170,66 +7857,92 @@
       <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
         <v>0.967</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
       <c r="L65" t="n">
-        <v>0.754</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="N65" t="n">
         <v>21</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>2.183</v>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q65" t="n">
-        <v>612.7938</v>
+        <v>2.189</v>
       </c>
       <c r="R65" t="n">
-        <v>718.1178</v>
+        <v>612.3687</v>
       </c>
       <c r="S65" t="n">
+        <v>717.6196</v>
+      </c>
+      <c r="T65" t="n">
         <v>228</v>
       </c>
-      <c r="T65" t="n">
+      <c r="U65" t="n">
         <v>267.1875</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.1</v>
       </c>
-      <c r="V65" t="n">
-        <v>2.6877</v>
-      </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr">
+      <c r="W65" t="n">
+        <v>2.6858</v>
+      </c>
+      <c r="X65" t="n">
+        <v>614.6655</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>720.3111</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.2968</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6258,66 +7971,92 @@
       <c r="F66" t="n">
         <v>1</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
         <v>0.948</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
       <c r="L66" t="n">
-        <v>0.784</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N66" t="n">
         <v>11</v>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>1.81</v>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q66" t="n">
-        <v>628.1025</v>
+        <v>1.812</v>
       </c>
       <c r="R66" t="n">
-        <v>886.2134</v>
+        <v>626.2491</v>
       </c>
       <c r="S66" t="n">
+        <v>883.5983</v>
+      </c>
+      <c r="T66" t="n">
         <v>164</v>
       </c>
-      <c r="T66" t="n">
+      <c r="U66" t="n">
         <v>231.3937</v>
       </c>
-      <c r="U66" t="n">
-        <v>0.215</v>
-      </c>
       <c r="V66" t="n">
-        <v>3.8299</v>
-      </c>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr">
+        <v>0.22</v>
+      </c>
+      <c r="W66" t="n">
+        <v>3.8186</v>
+      </c>
+      <c r="X66" t="n">
+        <v>619.3395</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>873.8493</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>6.9096</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>9.7491</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6346,66 +8085,92 @@
       <c r="F67" t="n">
         <v>1</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
         <v>0.971</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="N67" t="n">
         <v>12</v>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>牙位(上顎冠朝下)</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>2.563</v>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="Q67" t="n">
-        <v>598.3767</v>
+        <v>2.543</v>
       </c>
       <c r="R67" t="n">
-        <v>768.5401000000001</v>
+        <v>599.2693</v>
       </c>
       <c r="S67" t="n">
+        <v>769.6866</v>
+      </c>
+      <c r="T67" t="n">
         <v>208</v>
       </c>
-      <c r="T67" t="n">
+      <c r="U67" t="n">
         <v>267.15</v>
       </c>
-      <c r="U67" t="n">
-        <v>0.13</v>
-      </c>
       <c r="V67" t="n">
-        <v>2.8768</v>
-      </c>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr">
+        <v>0.158</v>
+      </c>
+      <c r="W67" t="n">
+        <v>2.8811</v>
+      </c>
+      <c r="X67" t="n">
+        <v>604.9016</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>776.9204999999999</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>5.6323</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>7.234</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6434,70 +8199,96 @@
       <c r="F68" t="n">
         <v>1</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>gt_iou</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>seg</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
         <v>0.979</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
       <c r="L68" t="n">
-        <v>0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="N68" t="n">
         <v>31</v>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>牙位(下顎冠朝上)</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
         <v>1.899</v>
       </c>
-      <c r="Q68" t="n">
-        <v>599.7036000000001</v>
-      </c>
       <c r="R68" t="n">
-        <v>1074.7814</v>
+        <v>599.6571</v>
       </c>
       <c r="S68" t="n">
-        <v>157.5</v>
+        <v>1074.698</v>
       </c>
       <c r="T68" t="n">
-        <v>282.2695</v>
+        <v>157</v>
       </c>
       <c r="U68" t="n">
-        <v>0.099</v>
+        <v>281.3734</v>
       </c>
       <c r="V68" t="n">
-        <v>3.8076</v>
-      </c>
-      <c r="W68" t="inlineStr">
+        <v>0.081</v>
+      </c>
+      <c r="W68" t="n">
+        <v>3.8195</v>
+      </c>
+      <c r="X68" t="n">
+        <v>601.6691</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1078.3038</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2.0119</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3.6058</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
         <is>
           <t>冠寬位置異常</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="AF68" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
@@ -6514,36 +8305,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>圖上顏色</t>
+          <t>空間</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>代表什麼</t>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>剔除碎塊</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>有效張數</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>長度MAE px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>長度偏差(bias) px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>誤差標準差 px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>最大絕對誤差 px</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>橘黃輪廓</t>
+          <t>letterbox</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>選中的 mask(seg 預測)</t>
-        </is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.619</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.519</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14.173</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15.196</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.572</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.955</v>
+      </c>
+      <c r="H3" t="n">
+        <v>104.805</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>圖上顏色</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>代表什麼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橘黃輪廓</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>選中的 mask(seg 預測)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>灰色輪廓</t>
         </is>
       </c>
@@ -6585,7 +8492,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GT 人工標註的 A/B(僅 pose 格式標註有)</t>
+          <t>GT 的 A/B(pose 標註點，或由 GT 多邊形以同一套幾何算出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>左上綠字</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B2 的逐張 mAP50-95、|ΔAB| = |預測長度 − GT 長度|(原圖 px)</t>
         </is>
       </c>
     </row>
